--- a/artfynd/A 21557-2020 artfynd.xlsx
+++ b/artfynd/A 21557-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21557-2020 artfynd.xlsx
+++ b/artfynd/A 21557-2020 artfynd.xlsx
@@ -14926,7 +14926,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119603728</v>
+        <v>119605419</v>
       </c>
       <c r="B112" t="n">
         <v>90562</v>
@@ -14959,20 +14959,29 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kungshamn-Morga naturreservat, Kungshamn-Morga naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>649082</v>
+        <v>649175</v>
       </c>
       <c r="R112" t="n">
-        <v>6629346</v>
+        <v>6629332</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -15048,7 +15057,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119605419</v>
+        <v>119603728</v>
       </c>
       <c r="B113" t="n">
         <v>90562</v>
@@ -15081,29 +15090,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kungshamn-Morga naturreservat, Kungshamn-Morga naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>649175</v>
+        <v>649082</v>
       </c>
       <c r="R113" t="n">
-        <v>6629332</v>
+        <v>6629346</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -15179,10 +15179,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119604982</v>
+        <v>119604578</v>
       </c>
       <c r="B114" t="n">
-        <v>100080</v>
+        <v>91290</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -15191,40 +15191,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222771</v>
+        <v>1105</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -15233,10 +15228,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>649087</v>
+        <v>649095</v>
       </c>
       <c r="R114" t="n">
-        <v>6629365</v>
+        <v>6629349</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15271,6 +15266,11 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Växer på exponerad ved på en ganska kraftig granlåga som börjar bli mjuk. Lyser upp rosa i ljuset från eftermiddagssolen.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -15279,6 +15279,26 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -15295,10 +15315,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119604578</v>
+        <v>119604982</v>
       </c>
       <c r="B115" t="n">
-        <v>91290</v>
+        <v>100080</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -15307,35 +15327,40 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1105</v>
+        <v>222771</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -15344,10 +15369,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649095</v>
+        <v>649087</v>
       </c>
       <c r="R115" t="n">
-        <v>6629349</v>
+        <v>6629365</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15382,11 +15407,6 @@
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Växer på exponerad ved på en ganska kraftig granlåga som börjar bli mjuk. Lyser upp rosa i ljuset från eftermiddagssolen.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -15395,26 +15415,6 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">

--- a/artfynd/A 21557-2020 artfynd.xlsx
+++ b/artfynd/A 21557-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15429,6 +15429,218 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120462703</v>
+      </c>
+      <c r="B116" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Kungshamn-Morga NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>649196</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6629305</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120462379</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Kungshamn-Morga NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>649144</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6629528</v>
+      </c>
+      <c r="S117" t="n">
+        <v>25</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21557-2020 artfynd.xlsx
+++ b/artfynd/A 21557-2020 artfynd.xlsx
@@ -15431,10 +15431,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120462703</v>
+        <v>120462379</v>
       </c>
       <c r="B116" t="n">
-        <v>90580</v>
+        <v>91200</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15443,25 +15443,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15474,10 +15474,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649196</v>
+        <v>649144</v>
       </c>
       <c r="R116" t="n">
-        <v>6629305</v>
+        <v>6629528</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -15537,10 +15537,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120462379</v>
+        <v>120462703</v>
       </c>
       <c r="B117" t="n">
-        <v>91200</v>
+        <v>90580</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15549,25 +15549,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649144</v>
+        <v>649196</v>
       </c>
       <c r="R117" t="n">
-        <v>6629528</v>
+        <v>6629305</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>

--- a/artfynd/A 21557-2020 artfynd.xlsx
+++ b/artfynd/A 21557-2020 artfynd.xlsx
@@ -15431,10 +15431,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120462379</v>
+        <v>120462703</v>
       </c>
       <c r="B116" t="n">
-        <v>91200</v>
+        <v>90580</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -15443,25 +15443,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -15474,10 +15474,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649144</v>
+        <v>649196</v>
       </c>
       <c r="R116" t="n">
-        <v>6629528</v>
+        <v>6629305</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -15537,10 +15537,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120462703</v>
+        <v>120462379</v>
       </c>
       <c r="B117" t="n">
-        <v>90580</v>
+        <v>91200</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -15549,25 +15549,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649196</v>
+        <v>649144</v>
       </c>
       <c r="R117" t="n">
-        <v>6629305</v>
+        <v>6629528</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>

--- a/artfynd/A 21557-2020 artfynd.xlsx
+++ b/artfynd/A 21557-2020 artfynd.xlsx
@@ -15646,7 +15646,7 @@
         <v>120899575</v>
       </c>
       <c r="B118" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
